--- a/Task5.xlsx
+++ b/Task5.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gayathri\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gayathri\Desktop\Coding Challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08ACA18-84AB-45AB-880D-7D7277B46687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCEC98A-589D-457B-BC4A-7C141E283820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Task5" sheetId="1" r:id="rId1"/>
     <sheet name="observations" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -867,9 +867,6 @@
     <t>ID only</t>
   </si>
   <si>
-    <t>I used left() for first name column</t>
-  </si>
-  <si>
     <t>I used right() to display emp id only</t>
   </si>
   <si>
@@ -895,6 +892,9 @@
   </si>
   <si>
     <t>I used proper() to display names in again proper format</t>
+  </si>
+  <si>
+    <t>I used left() for first name column but it does not come with full first name so I used iferror(left()).</t>
   </si>
 </sst>
 </file>
@@ -976,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -986,9 +986,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -1009,7 +1006,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1021,8 +1018,43 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1053,41 +1085,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1102,23 +1099,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{94CCACD2-6A4C-46D2-B99C-A54BC4A84DB8}" name="Table1" displayName="Table1" ref="A1:M151" totalsRowShown="0" headerRowDxfId="7" dataDxfId="8" headerRowBorderDxfId="15" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{94CCACD2-6A4C-46D2-B99C-A54BC4A84DB8}" name="Table1" displayName="Table1" ref="A1:M151" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="A1:M151" xr:uid="{94CCACD2-6A4C-46D2-B99C-A54BC4A84DB8}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{41CC4607-4258-4674-897F-93982336E608}" name="Employee ID" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{0C3921A1-73C1-46E8-8E7F-66F1E3C032EC}" name="Name" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{01CD3F61-3EEB-41CB-870B-9C709546CD8C}" name="Department" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{78E0DF4D-EEEB-4039-AA72-4F1EA90A782F}" name="Country" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{14EAA116-3D44-4C1D-A37B-148AA67E1686}" name="Salary" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{27E50B58-3BD2-408D-ADBC-10F6FCF29D1A}" name="Date of Joining" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{7AF640D0-0DCE-4660-A420-11F72B31DEF5}" name="Email" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{DB21574E-355E-4FE4-BC6F-CFDDE707A547}" name="First Name" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{41CC4607-4258-4674-897F-93982336E608}" name="Employee ID" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{0C3921A1-73C1-46E8-8E7F-66F1E3C032EC}" name="Name" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{01CD3F61-3EEB-41CB-870B-9C709546CD8C}" name="Department" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{78E0DF4D-EEEB-4039-AA72-4F1EA90A782F}" name="Country" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{14EAA116-3D44-4C1D-A37B-148AA67E1686}" name="Salary" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{27E50B58-3BD2-408D-ADBC-10F6FCF29D1A}" name="Date of Joining" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{7AF640D0-0DCE-4660-A420-11F72B31DEF5}" name="Email" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{DB21574E-355E-4FE4-BC6F-CFDDE707A547}" name="First Name" dataDxfId="5">
       <calculatedColumnFormula>LEFT(F2, 4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F238789E-E65B-4060-A4AE-D64664E94A8F}" name="ID only" dataDxfId="5">
+    <tableColumn id="11" xr3:uid="{F238789E-E65B-4060-A4AE-D64664E94A8F}" name="ID only" dataDxfId="4">
       <calculatedColumnFormula>RIGHT(A2,4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D110E08B-8EF1-41C6-B026-03AC1F910680}" name="userid" dataDxfId="4">
+    <tableColumn id="12" xr3:uid="{D110E08B-8EF1-41C6-B026-03AC1F910680}" name="userid" dataDxfId="3">
       <calculatedColumnFormula>MID(F3,6,5)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{7B169543-92FF-4CBE-A51B-B83D526B97E8}" name="Names in CAPS" dataDxfId="2">
@@ -1470,16 +1467,16 @@
         <v>276</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1506,15 +1503,15 @@
         <f t="shared" ref="I2:I33" si="0">RIGHT(A2,4)</f>
         <v>1000</v>
       </c>
-      <c r="K2" s="4" t="str">
+      <c r="K2" s="1" t="str">
         <f t="shared" ref="K2:K33" si="1">UPPER(B2)</f>
         <v/>
       </c>
-      <c r="L2" s="4" t="str">
+      <c r="L2" s="1" t="str">
         <f t="shared" ref="L2:L33" si="2">LOWER(D2)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M2" s="4" t="str">
+      <c r="M2" s="1" t="str">
         <f t="shared" ref="M2:M33" si="3">PROPER(K2)</f>
         <v/>
       </c>
@@ -1542,7 +1539,7 @@
         <v>177</v>
       </c>
       <c r="H3" s="1" t="str">
-        <f>LEFT(B3,3)</f>
+        <f>IFERROR(LEFT(B3, FIND(" ", B3) - 1), B3)</f>
         <v>Eve</v>
       </c>
       <c r="I3" s="1" t="str">
@@ -1553,15 +1550,15 @@
         <f>MID(G3,1,7)</f>
         <v>user106</v>
       </c>
-      <c r="K3" s="4" t="str">
+      <c r="K3" s="1" t="str">
         <f t="shared" si="1"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L3" s="4" t="str">
+      <c r="L3" s="1" t="str">
         <f t="shared" si="2"/>
         <v>germany</v>
       </c>
-      <c r="M3" s="4" t="str">
+      <c r="M3" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Eve Adams</v>
       </c>
@@ -1589,7 +1586,7 @@
         <v>178</v>
       </c>
       <c r="H4" s="1" t="str">
-        <f>LEFT(B4,5)</f>
+        <f t="shared" ref="H4:H67" si="4">IFERROR(LEFT(B4, FIND(" ", B4) - 1), B4)</f>
         <v>Alice</v>
       </c>
       <c r="I4" s="1" t="str">
@@ -1597,18 +1594,18 @@
         <v>1002</v>
       </c>
       <c r="J4" s="1" t="str">
-        <f t="shared" ref="J4:J67" si="4">MID(G4,1,7)</f>
+        <f t="shared" ref="J4:J67" si="5">MID(G4,1,7)</f>
         <v>user176</v>
       </c>
-      <c r="K4" s="4" t="str">
+      <c r="K4" s="1" t="str">
         <f t="shared" si="1"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L4" s="4" t="str">
+      <c r="L4" s="1" t="str">
         <f t="shared" si="2"/>
         <v>germany</v>
       </c>
-      <c r="M4" s="4" t="str">
+      <c r="M4" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Alice Brown</v>
       </c>
@@ -1636,26 +1633,26 @@
         <v>179</v>
       </c>
       <c r="H5" s="1" t="str">
-        <f>LEFT(B5,5)</f>
-        <v xml:space="preserve">John </v>
+        <f t="shared" si="4"/>
+        <v>John</v>
       </c>
       <c r="I5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="J5" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user168</v>
       </c>
-      <c r="K5" s="4" t="str">
+      <c r="K5" s="1" t="str">
         <f t="shared" si="1"/>
         <v>JOHN DOE</v>
       </c>
-      <c r="L5" s="4" t="str">
+      <c r="L5" s="1" t="str">
         <f t="shared" si="2"/>
         <v>usa</v>
       </c>
-      <c r="M5" s="4" t="str">
+      <c r="M5" s="1" t="str">
         <f t="shared" si="3"/>
         <v>John Doe</v>
       </c>
@@ -1683,26 +1680,26 @@
         <v>180</v>
       </c>
       <c r="H6" s="1" t="str">
-        <f>LEFT(B6,3)</f>
-        <v>Jan</v>
+        <f t="shared" si="4"/>
+        <v>Jane</v>
       </c>
       <c r="I6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="J6" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user49@</v>
       </c>
-      <c r="K6" s="4" t="str">
+      <c r="K6" s="1" t="str">
         <f t="shared" si="1"/>
         <v>JANE SMITH</v>
       </c>
-      <c r="L6" s="4" t="str">
+      <c r="L6" s="1" t="str">
         <f t="shared" si="2"/>
         <v>germany</v>
       </c>
-      <c r="M6" s="4" t="str">
+      <c r="M6" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Jane Smith</v>
       </c>
@@ -1730,26 +1727,26 @@
         <v>181</v>
       </c>
       <c r="H7" s="1" t="str">
-        <f>LEFT(B7,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="J7" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user24@</v>
       </c>
-      <c r="K7" s="4" t="str">
+      <c r="K7" s="1" t="str">
         <f t="shared" si="1"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L7" s="4" t="str">
+      <c r="L7" s="1" t="str">
         <f t="shared" si="2"/>
         <v>india</v>
       </c>
-      <c r="M7" s="4" t="str">
+      <c r="M7" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Alice Brown</v>
       </c>
@@ -1774,7 +1771,7 @@
         <v>179</v>
       </c>
       <c r="H8" s="1" t="str">
-        <f>LEFT(B8,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I8" s="1" t="str">
@@ -1782,18 +1779,18 @@
         <v>1006</v>
       </c>
       <c r="J8" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user168</v>
       </c>
-      <c r="K8" s="4" t="str">
+      <c r="K8" s="1" t="str">
         <f t="shared" si="1"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L8" s="4" t="str">
+      <c r="L8" s="1" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M8" s="4" t="str">
+      <c r="M8" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Sam Wilson</v>
       </c>
@@ -1818,26 +1815,26 @@
         <v>182</v>
       </c>
       <c r="H9" s="1" t="str">
-        <f>LEFT(B9,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
       <c r="J9" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user26@</v>
       </c>
-      <c r="K9" s="4" t="str">
+      <c r="K9" s="1" t="str">
         <f t="shared" si="1"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L9" s="4" t="str">
+      <c r="L9" s="1" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M9" s="4" t="str">
+      <c r="M9" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Chris Lee</v>
       </c>
@@ -1865,26 +1862,26 @@
         <v>183</v>
       </c>
       <c r="H10" s="1" t="str">
-        <f>LEFT(B10,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
       <c r="J10" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user25@</v>
       </c>
-      <c r="K10" s="4" t="str">
+      <c r="K10" s="1" t="str">
         <f t="shared" si="1"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L10" s="4" t="str">
+      <c r="L10" s="1" t="str">
         <f t="shared" si="2"/>
         <v>germany</v>
       </c>
-      <c r="M10" s="4" t="str">
+      <c r="M10" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Alice Brown</v>
       </c>
@@ -1912,26 +1909,26 @@
         <v>184</v>
       </c>
       <c r="H11" s="1" t="str">
-        <f>LEFT(B11,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1009</v>
       </c>
       <c r="J11" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user153</v>
       </c>
-      <c r="K11" s="4" t="str">
+      <c r="K11" s="1" t="str">
         <f t="shared" si="1"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L11" s="4" t="str">
+      <c r="L11" s="1" t="str">
         <f t="shared" si="2"/>
         <v>uk</v>
       </c>
-      <c r="M11" s="4" t="str">
+      <c r="M11" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Chris Lee</v>
       </c>
@@ -1959,7 +1956,7 @@
         <v>185</v>
       </c>
       <c r="H12" s="1" t="str">
-        <f>LEFT(B12,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I12" s="1" t="str">
@@ -1967,18 +1964,18 @@
         <v>1010</v>
       </c>
       <c r="J12" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user18@</v>
       </c>
-      <c r="K12" s="4" t="str">
+      <c r="K12" s="1" t="str">
         <f t="shared" si="1"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L12" s="4" t="str">
+      <c r="L12" s="1" t="str">
         <f t="shared" si="2"/>
         <v>uk</v>
       </c>
-      <c r="M12" s="4" t="str">
+      <c r="M12" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Sam Wilson</v>
       </c>
@@ -2006,7 +2003,7 @@
         <v>186</v>
       </c>
       <c r="H13" s="1" t="str">
-        <f>LEFT(B13,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I13" s="1" t="str">
@@ -2014,18 +2011,18 @@
         <v>1011</v>
       </c>
       <c r="J13" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user1@e</v>
       </c>
-      <c r="K13" s="4" t="str">
+      <c r="K13" s="1" t="str">
         <f t="shared" si="1"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L13" s="4" t="str">
+      <c r="L13" s="1" t="str">
         <f t="shared" si="2"/>
         <v>usa</v>
       </c>
-      <c r="M13" s="4" t="str">
+      <c r="M13" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Sam Wilson</v>
       </c>
@@ -2050,7 +2047,7 @@
         <v>177</v>
       </c>
       <c r="H14" s="1" t="str">
-        <f>LEFT(B14,3)</f>
+        <f t="shared" si="4"/>
         <v>Bob</v>
       </c>
       <c r="I14" s="1" t="str">
@@ -2058,18 +2055,18 @@
         <v>1012</v>
       </c>
       <c r="J14" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user106</v>
       </c>
-      <c r="K14" s="4" t="str">
+      <c r="K14" s="1" t="str">
         <f t="shared" si="1"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L14" s="4" t="str">
+      <c r="L14" s="1" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M14" s="4" t="str">
+      <c r="M14" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Bob Johnson</v>
       </c>
@@ -2094,7 +2091,7 @@
         <v>187</v>
       </c>
       <c r="H15" s="1" t="str">
-        <f>LEFT(B15,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I15" s="1" t="str">
@@ -2102,18 +2099,18 @@
         <v>1013</v>
       </c>
       <c r="J15" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user180</v>
       </c>
-      <c r="K15" s="4" t="str">
+      <c r="K15" s="1" t="str">
         <f t="shared" si="1"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L15" s="4" t="str">
+      <c r="L15" s="1" t="str">
         <f t="shared" si="2"/>
         <v>india</v>
       </c>
-      <c r="M15" s="4" t="str">
+      <c r="M15" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Sam Wilson</v>
       </c>
@@ -2138,26 +2135,26 @@
         <v>188</v>
       </c>
       <c r="H16" s="1" t="str">
-        <f>LEFT(B16,3)</f>
-        <v>Jan</v>
+        <f t="shared" si="4"/>
+        <v>Jane</v>
       </c>
       <c r="I16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1014</v>
       </c>
       <c r="J16" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user184</v>
       </c>
-      <c r="K16" s="4" t="str">
+      <c r="K16" s="1" t="str">
         <f t="shared" si="1"/>
         <v>JANE SMITH</v>
       </c>
-      <c r="L16" s="4" t="str">
+      <c r="L16" s="1" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M16" s="4" t="str">
+      <c r="M16" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Jane Smith</v>
       </c>
@@ -2181,27 +2178,27 @@
       <c r="G17" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="H17" s="1" t="str">
-        <f>LEFT(B17,3)</f>
-        <v/>
+      <c r="H17" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="I17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1015</v>
       </c>
       <c r="J17" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user3@e</v>
       </c>
-      <c r="K17" s="4" t="str">
+      <c r="K17" s="1" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L17" s="4" t="str">
+      <c r="L17" s="1" t="str">
         <f t="shared" si="2"/>
         <v>india</v>
       </c>
-      <c r="M17" s="4" t="str">
+      <c r="M17" s="1" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2226,7 +2223,7 @@
         <v>190</v>
       </c>
       <c r="H18" s="1" t="str">
-        <f>LEFT(B18,3)</f>
+        <f t="shared" si="4"/>
         <v>Bob</v>
       </c>
       <c r="I18" s="1" t="str">
@@ -2234,18 +2231,18 @@
         <v>1016</v>
       </c>
       <c r="J18" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user64@</v>
       </c>
-      <c r="K18" s="4" t="str">
+      <c r="K18" s="1" t="str">
         <f t="shared" si="1"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L18" s="4" t="str">
+      <c r="L18" s="1" t="str">
         <f t="shared" si="2"/>
         <v>germany</v>
       </c>
-      <c r="M18" s="4" t="str">
+      <c r="M18" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Bob Johnson</v>
       </c>
@@ -2273,26 +2270,26 @@
         <v>191</v>
       </c>
       <c r="H19" s="1" t="str">
-        <f>LEFT(B19,3)</f>
-        <v>Jan</v>
+        <f t="shared" si="4"/>
+        <v>Jane</v>
       </c>
       <c r="I19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1017</v>
       </c>
       <c r="J19" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user38@</v>
       </c>
-      <c r="K19" s="4" t="str">
+      <c r="K19" s="1" t="str">
         <f t="shared" si="1"/>
         <v>JANE SMITH</v>
       </c>
-      <c r="L19" s="4" t="str">
+      <c r="L19" s="1" t="str">
         <f t="shared" si="2"/>
         <v>australia</v>
       </c>
-      <c r="M19" s="4" t="str">
+      <c r="M19" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Jane Smith</v>
       </c>
@@ -2320,26 +2317,26 @@
         <v>192</v>
       </c>
       <c r="H20" s="1" t="str">
-        <f>LEFT(B20,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1018</v>
       </c>
       <c r="J20" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user96@</v>
       </c>
-      <c r="K20" s="4" t="str">
+      <c r="K20" s="1" t="str">
         <f t="shared" si="1"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L20" s="4" t="str">
+      <c r="L20" s="1" t="str">
         <f t="shared" si="2"/>
         <v>uk</v>
       </c>
-      <c r="M20" s="4" t="str">
+      <c r="M20" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Alice Brown</v>
       </c>
@@ -2364,7 +2361,7 @@
         <v>193</v>
       </c>
       <c r="H21" s="1" t="str">
-        <f>LEFT(B21,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I21" s="1" t="str">
@@ -2372,18 +2369,18 @@
         <v>1019</v>
       </c>
       <c r="J21" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user151</v>
       </c>
-      <c r="K21" s="4" t="str">
+      <c r="K21" s="1" t="str">
         <f t="shared" si="1"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L21" s="4" t="str">
+      <c r="L21" s="1" t="str">
         <f t="shared" si="2"/>
         <v>india</v>
       </c>
-      <c r="M21" s="4" t="str">
+      <c r="M21" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Eve Adams</v>
       </c>
@@ -2411,26 +2408,26 @@
         <v>194</v>
       </c>
       <c r="H22" s="1" t="str">
-        <f>LEFT(B22,3)</f>
-        <v>Jan</v>
+        <f t="shared" si="4"/>
+        <v>Jane</v>
       </c>
       <c r="I22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
       <c r="J22" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user200</v>
       </c>
-      <c r="K22" s="4" t="str">
+      <c r="K22" s="1" t="str">
         <f t="shared" si="1"/>
         <v>JANE SMITH</v>
       </c>
-      <c r="L22" s="4" t="str">
+      <c r="L22" s="1" t="str">
         <f t="shared" si="2"/>
         <v>usa</v>
       </c>
-      <c r="M22" s="4" t="str">
+      <c r="M22" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Jane Smith</v>
       </c>
@@ -2455,26 +2452,26 @@
         <v>195</v>
       </c>
       <c r="H23" s="1" t="str">
-        <f>LEFT(B23,3)</f>
-        <v>Jan</v>
+        <f t="shared" si="4"/>
+        <v>Jane</v>
       </c>
       <c r="I23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1021</v>
       </c>
       <c r="J23" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user77@</v>
       </c>
-      <c r="K23" s="4" t="str">
+      <c r="K23" s="1" t="str">
         <f t="shared" si="1"/>
         <v>JANE SMITH</v>
       </c>
-      <c r="L23" s="4" t="str">
+      <c r="L23" s="1" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M23" s="4" t="str">
+      <c r="M23" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Jane Smith</v>
       </c>
@@ -2502,7 +2499,7 @@
         <v>196</v>
       </c>
       <c r="H24" s="1" t="str">
-        <f>LEFT(B24,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I24" s="1" t="str">
@@ -2510,18 +2507,18 @@
         <v>1022</v>
       </c>
       <c r="J24" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user128</v>
       </c>
-      <c r="K24" s="4" t="str">
+      <c r="K24" s="1" t="str">
         <f t="shared" si="1"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L24" s="4" t="str">
+      <c r="L24" s="1" t="str">
         <f t="shared" si="2"/>
         <v>india</v>
       </c>
-      <c r="M24" s="4" t="str">
+      <c r="M24" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Eve Adams</v>
       </c>
@@ -2549,26 +2546,26 @@
         <v>197</v>
       </c>
       <c r="H25" s="1" t="str">
-        <f>LEFT(B25,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1023</v>
       </c>
       <c r="J25" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user149</v>
       </c>
-      <c r="K25" s="4" t="str">
+      <c r="K25" s="1" t="str">
         <f t="shared" si="1"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L25" s="4" t="str">
+      <c r="L25" s="1" t="str">
         <f t="shared" si="2"/>
         <v>uk</v>
       </c>
-      <c r="M25" s="4" t="str">
+      <c r="M25" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Alice Brown</v>
       </c>
@@ -2593,7 +2590,7 @@
         <v>198</v>
       </c>
       <c r="H26" s="1" t="str">
-        <f>LEFT(B26,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I26" s="1" t="str">
@@ -2601,18 +2598,18 @@
         <v>1024</v>
       </c>
       <c r="J26" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user122</v>
       </c>
-      <c r="K26" s="4" t="str">
+      <c r="K26" s="1" t="str">
         <f t="shared" si="1"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L26" s="4" t="str">
+      <c r="L26" s="1" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M26" s="4" t="str">
+      <c r="M26" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Sam Wilson</v>
       </c>
@@ -2637,26 +2634,26 @@
         <v>199</v>
       </c>
       <c r="H27" s="1" t="str">
-        <f>LEFT(B27,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1025</v>
       </c>
       <c r="J27" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user41@</v>
       </c>
-      <c r="K27" s="4" t="str">
+      <c r="K27" s="1" t="str">
         <f t="shared" si="1"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L27" s="4" t="str">
+      <c r="L27" s="1" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M27" s="4" t="str">
+      <c r="M27" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Chris Lee</v>
       </c>
@@ -2684,7 +2681,7 @@
         <v>200</v>
       </c>
       <c r="H28" s="1" t="str">
-        <f>LEFT(B28,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I28" s="1" t="str">
@@ -2692,18 +2689,18 @@
         <v>1026</v>
       </c>
       <c r="J28" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user68@</v>
       </c>
-      <c r="K28" s="4" t="str">
+      <c r="K28" s="1" t="str">
         <f t="shared" si="1"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L28" s="4" t="str">
+      <c r="L28" s="1" t="str">
         <f t="shared" si="2"/>
         <v>germany</v>
       </c>
-      <c r="M28" s="4" t="str">
+      <c r="M28" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Eve Adams</v>
       </c>
@@ -2731,26 +2728,26 @@
         <v>201</v>
       </c>
       <c r="H29" s="1" t="str">
-        <f>LEFT(B29,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1027</v>
       </c>
       <c r="J29" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user103</v>
       </c>
-      <c r="K29" s="4" t="str">
+      <c r="K29" s="1" t="str">
         <f t="shared" si="1"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L29" s="4" t="str">
+      <c r="L29" s="1" t="str">
         <f t="shared" si="2"/>
         <v>uk</v>
       </c>
-      <c r="M29" s="4" t="str">
+      <c r="M29" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Alice Brown</v>
       </c>
@@ -2778,26 +2775,26 @@
         <v>202</v>
       </c>
       <c r="H30" s="1" t="str">
-        <f>LEFT(B30,3)</f>
-        <v>Joh</v>
+        <f t="shared" si="4"/>
+        <v>John</v>
       </c>
       <c r="I30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1028</v>
       </c>
       <c r="J30" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user135</v>
       </c>
-      <c r="K30" s="4" t="str">
+      <c r="K30" s="1" t="str">
         <f t="shared" si="1"/>
         <v>JOHN DOE</v>
       </c>
-      <c r="L30" s="4" t="str">
+      <c r="L30" s="1" t="str">
         <f t="shared" si="2"/>
         <v>uk</v>
       </c>
-      <c r="M30" s="4" t="str">
+      <c r="M30" s="1" t="str">
         <f t="shared" si="3"/>
         <v>John Doe</v>
       </c>
@@ -2825,7 +2822,7 @@
         <v>203</v>
       </c>
       <c r="H31" s="1" t="str">
-        <f>LEFT(B31,3)</f>
+        <f t="shared" si="4"/>
         <v>Bob</v>
       </c>
       <c r="I31" s="1" t="str">
@@ -2833,18 +2830,18 @@
         <v>1029</v>
       </c>
       <c r="J31" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user83@</v>
       </c>
-      <c r="K31" s="4" t="str">
+      <c r="K31" s="1" t="str">
         <f t="shared" si="1"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L31" s="4" t="str">
+      <c r="L31" s="1" t="str">
         <f t="shared" si="2"/>
         <v>uk</v>
       </c>
-      <c r="M31" s="4" t="str">
+      <c r="M31" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Bob Johnson</v>
       </c>
@@ -2862,27 +2859,27 @@
       <c r="G32" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="H32" s="1" t="str">
-        <f>LEFT(B32,3)</f>
-        <v/>
+      <c r="H32" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="I32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1030</v>
       </c>
       <c r="J32" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user109</v>
       </c>
-      <c r="K32" s="4" t="str">
+      <c r="K32" s="1" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L32" s="4" t="str">
+      <c r="L32" s="1" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M32" s="4" t="str">
+      <c r="M32" s="1" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2910,7 +2907,7 @@
         <v>205</v>
       </c>
       <c r="H33" s="1" t="str">
-        <f>LEFT(B33,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I33" s="1" t="str">
@@ -2918,18 +2915,18 @@
         <v>1031</v>
       </c>
       <c r="J33" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user143</v>
       </c>
-      <c r="K33" s="4" t="str">
+      <c r="K33" s="1" t="str">
         <f t="shared" si="1"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L33" s="4" t="str">
+      <c r="L33" s="1" t="str">
         <f t="shared" si="2"/>
         <v>germany</v>
       </c>
-      <c r="M33" s="4" t="str">
+      <c r="M33" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Eve Adams</v>
       </c>
@@ -2954,27 +2951,27 @@
         <v>206</v>
       </c>
       <c r="H34" s="1" t="str">
-        <f>LEFT(B34,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I34" s="1" t="str">
-        <f t="shared" ref="I34:I65" si="5">RIGHT(A34,4)</f>
+        <f t="shared" ref="I34:I65" si="6">RIGHT(A34,4)</f>
         <v>1032</v>
       </c>
       <c r="J34" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user190</v>
       </c>
-      <c r="K34" s="4" t="str">
-        <f t="shared" ref="K34:K65" si="6">UPPER(B34)</f>
+      <c r="K34" s="1" t="str">
+        <f t="shared" ref="K34:K65" si="7">UPPER(B34)</f>
         <v>SAM WILSON</v>
       </c>
-      <c r="L34" s="4" t="str">
-        <f t="shared" ref="L34:L65" si="7">LOWER(D34)</f>
+      <c r="L34" s="1" t="str">
+        <f t="shared" ref="L34:L65" si="8">LOWER(D34)</f>
         <v/>
       </c>
-      <c r="M34" s="4" t="str">
-        <f t="shared" ref="M34:M65" si="8">PROPER(K34)</f>
+      <c r="M34" s="1" t="str">
+        <f t="shared" ref="M34:M65" si="9">PROPER(K34)</f>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -2998,27 +2995,27 @@
         <v>207</v>
       </c>
       <c r="H35" s="1" t="str">
-        <f>LEFT(B35,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I35" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1033</v>
+      </c>
+      <c r="J35" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1033</v>
-      </c>
-      <c r="J35" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user136</v>
       </c>
-      <c r="K35" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K35" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L35" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L35" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>usa</v>
       </c>
-      <c r="M35" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M35" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -3045,27 +3042,27 @@
         <v>208</v>
       </c>
       <c r="H36" s="1" t="str">
-        <f>LEFT(B36,3)</f>
-        <v>Joh</v>
+        <f t="shared" si="4"/>
+        <v>John</v>
       </c>
       <c r="I36" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1034</v>
+      </c>
+      <c r="J36" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1034</v>
-      </c>
-      <c r="J36" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user198</v>
       </c>
-      <c r="K36" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K36" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>JOHN DOE</v>
       </c>
-      <c r="L36" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L36" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>australia</v>
       </c>
-      <c r="M36" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M36" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -3089,27 +3086,27 @@
         <v>176</v>
       </c>
       <c r="H37" s="1" t="str">
-        <f>LEFT(B37,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I37" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1035</v>
+      </c>
+      <c r="J37" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1035</v>
-      </c>
-      <c r="J37" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>invalid</v>
       </c>
-      <c r="K37" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K37" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L37" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L37" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>uk</v>
       </c>
-      <c r="M37" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M37" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -3136,27 +3133,27 @@
         <v>209</v>
       </c>
       <c r="H38" s="1" t="str">
-        <f>LEFT(B38,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I38" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1036</v>
+      </c>
+      <c r="J38" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1036</v>
-      </c>
-      <c r="J38" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user31@</v>
       </c>
-      <c r="K38" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K38" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L38" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L38" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>usa</v>
       </c>
-      <c r="M38" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M38" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -3180,27 +3177,27 @@
         <v>210</v>
       </c>
       <c r="H39" s="1" t="str">
-        <f>LEFT(B39,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I39" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1037</v>
+      </c>
+      <c r="J39" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1037</v>
-      </c>
-      <c r="J39" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user98@</v>
       </c>
-      <c r="K39" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K39" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L39" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L39" s="1" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M39" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M39" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -3227,27 +3224,27 @@
         <v>211</v>
       </c>
       <c r="H40" s="1" t="str">
-        <f>LEFT(B40,3)</f>
-        <v>Joh</v>
+        <f t="shared" si="4"/>
+        <v>John</v>
       </c>
       <c r="I40" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1038</v>
+      </c>
+      <c r="J40" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1038</v>
-      </c>
-      <c r="J40" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user154</v>
       </c>
-      <c r="K40" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K40" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>JOHN DOE</v>
       </c>
-      <c r="L40" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L40" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>uk</v>
       </c>
-      <c r="M40" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M40" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -3274,27 +3271,27 @@
         <v>212</v>
       </c>
       <c r="H41" s="1" t="str">
-        <f>LEFT(B41,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I41" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1039</v>
+      </c>
+      <c r="J41" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1039</v>
-      </c>
-      <c r="J41" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user42@</v>
       </c>
-      <c r="K41" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K41" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L41" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L41" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>uk</v>
       </c>
-      <c r="M41" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M41" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -3318,27 +3315,27 @@
         <v>213</v>
       </c>
       <c r="H42" s="1" t="str">
-        <f>LEFT(B42,3)</f>
+        <f t="shared" si="4"/>
         <v>Bob</v>
       </c>
       <c r="I42" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1040</v>
+      </c>
+      <c r="J42" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1040</v>
-      </c>
-      <c r="J42" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user89@</v>
       </c>
-      <c r="K42" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K42" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L42" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L42" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>uk</v>
       </c>
-      <c r="M42" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M42" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -3365,27 +3362,27 @@
         <v>214</v>
       </c>
       <c r="H43" s="1" t="str">
-        <f>LEFT(B43,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I43" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1041</v>
+      </c>
+      <c r="J43" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1041</v>
-      </c>
-      <c r="J43" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user47@</v>
       </c>
-      <c r="K43" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K43" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L43" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L43" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>germany</v>
       </c>
-      <c r="M43" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M43" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -3409,27 +3406,27 @@
         <v>215</v>
       </c>
       <c r="H44" s="1" t="str">
-        <f>LEFT(B44,3)</f>
+        <f t="shared" si="4"/>
         <v>Bob</v>
       </c>
       <c r="I44" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1042</v>
+      </c>
+      <c r="J44" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1042</v>
-      </c>
-      <c r="J44" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user175</v>
       </c>
-      <c r="K44" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K44" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L44" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L44" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>australia</v>
       </c>
-      <c r="M44" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M44" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -3456,27 +3453,27 @@
         <v>216</v>
       </c>
       <c r="H45" s="1" t="str">
-        <f>LEFT(B45,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="4"/>
+        <v>Alice</v>
       </c>
       <c r="I45" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1043</v>
+      </c>
+      <c r="J45" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1043</v>
-      </c>
-      <c r="J45" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user57@</v>
       </c>
-      <c r="K45" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K45" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L45" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L45" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>australia</v>
       </c>
-      <c r="M45" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M45" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -3500,27 +3497,27 @@
         <v>217</v>
       </c>
       <c r="H46" s="1" t="str">
-        <f>LEFT(B46,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I46" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1044</v>
+      </c>
+      <c r="J46" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1044</v>
-      </c>
-      <c r="J46" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user20@</v>
       </c>
-      <c r="K46" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K46" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L46" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L46" s="1" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M46" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M46" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -3540,28 +3537,28 @@
       <c r="G47" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H47" s="1" t="str">
-        <f>LEFT(B47,3)</f>
-        <v/>
+      <c r="H47" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="I47" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1045</v>
+      </c>
+      <c r="J47" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1045</v>
-      </c>
-      <c r="J47" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user106</v>
       </c>
-      <c r="K47" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="L47" s="4" t="str">
+      <c r="K47" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M47" s="4" t="str">
+      <c r="L47" s="1" t="str">
         <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="M47" s="1" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3588,27 +3585,27 @@
         <v>218</v>
       </c>
       <c r="H48" s="1" t="str">
-        <f>LEFT(B48,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I48" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1046</v>
+      </c>
+      <c r="J48" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1046</v>
-      </c>
-      <c r="J48" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user199</v>
       </c>
-      <c r="K48" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K48" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L48" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L48" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>germany</v>
       </c>
-      <c r="M48" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M48" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -3635,27 +3632,27 @@
         <v>219</v>
       </c>
       <c r="H49" s="1" t="str">
-        <f>LEFT(B49,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I49" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1047</v>
+      </c>
+      <c r="J49" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1047</v>
-      </c>
-      <c r="J49" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user43@</v>
       </c>
-      <c r="K49" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K49" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L49" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L49" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>india</v>
       </c>
-      <c r="M49" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M49" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -3679,27 +3676,27 @@
         <v>181</v>
       </c>
       <c r="H50" s="1" t="str">
-        <f>LEFT(B50,3)</f>
-        <v>Joh</v>
+        <f t="shared" si="4"/>
+        <v>John</v>
       </c>
       <c r="I50" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1048</v>
+      </c>
+      <c r="J50" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1048</v>
-      </c>
-      <c r="J50" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user24@</v>
       </c>
-      <c r="K50" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K50" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>JOHN DOE</v>
       </c>
-      <c r="L50" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L50" s="1" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M50" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M50" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -3726,27 +3723,27 @@
         <v>213</v>
       </c>
       <c r="H51" s="1" t="str">
-        <f>LEFT(B51,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I51" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1049</v>
+      </c>
+      <c r="J51" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1049</v>
-      </c>
-      <c r="J51" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user89@</v>
       </c>
-      <c r="K51" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K51" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L51" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L51" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>germany</v>
       </c>
-      <c r="M51" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M51" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -3767,27 +3764,27 @@
         <v>220</v>
       </c>
       <c r="H52" s="1" t="str">
-        <f>LEFT(B52,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I52" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1050</v>
+      </c>
+      <c r="J52" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1050</v>
-      </c>
-      <c r="J52" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user95@</v>
       </c>
-      <c r="K52" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K52" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L52" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L52" s="1" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M52" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M52" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -3814,27 +3811,27 @@
         <v>221</v>
       </c>
       <c r="H53" s="1" t="str">
-        <f>LEFT(B53,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I53" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1051</v>
+      </c>
+      <c r="J53" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1051</v>
-      </c>
-      <c r="J53" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user59@</v>
       </c>
-      <c r="K53" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K53" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L53" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L53" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>india</v>
       </c>
-      <c r="M53" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M53" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -3858,27 +3855,27 @@
         <v>222</v>
       </c>
       <c r="H54" s="1" t="str">
-        <f>LEFT(B54,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I54" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1052</v>
+      </c>
+      <c r="J54" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1052</v>
-      </c>
-      <c r="J54" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user152</v>
       </c>
-      <c r="K54" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K54" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L54" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L54" s="1" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M54" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M54" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -3905,27 +3902,27 @@
         <v>194</v>
       </c>
       <c r="H55" s="1" t="str">
-        <f>LEFT(B55,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I55" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1053</v>
+      </c>
+      <c r="J55" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1053</v>
-      </c>
-      <c r="J55" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user200</v>
       </c>
-      <c r="K55" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K55" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L55" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L55" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>uk</v>
       </c>
-      <c r="M55" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M55" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -3952,27 +3949,27 @@
         <v>223</v>
       </c>
       <c r="H56" s="1" t="str">
-        <f>LEFT(B56,3)</f>
+        <f t="shared" si="4"/>
         <v>Bob</v>
       </c>
       <c r="I56" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1054</v>
+      </c>
+      <c r="J56" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1054</v>
-      </c>
-      <c r="J56" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user92@</v>
       </c>
-      <c r="K56" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K56" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L56" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L56" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>uk</v>
       </c>
-      <c r="M56" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M56" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -3996,27 +3993,27 @@
         <v>224</v>
       </c>
       <c r="H57" s="1" t="str">
-        <f>LEFT(B57,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I57" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1055</v>
+      </c>
+      <c r="J57" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1055</v>
-      </c>
-      <c r="J57" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user50@</v>
       </c>
-      <c r="K57" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K57" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L57" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L57" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>usa</v>
       </c>
-      <c r="M57" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M57" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -4043,27 +4040,27 @@
         <v>225</v>
       </c>
       <c r="H58" s="1" t="str">
-        <f>LEFT(B58,3)</f>
-        <v>Joh</v>
+        <f t="shared" si="4"/>
+        <v>John</v>
       </c>
       <c r="I58" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1056</v>
+      </c>
+      <c r="J58" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1056</v>
-      </c>
-      <c r="J58" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user63@</v>
       </c>
-      <c r="K58" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K58" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>JOHN DOE</v>
       </c>
-      <c r="L58" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L58" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>australia</v>
       </c>
-      <c r="M58" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M58" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -4087,27 +4084,27 @@
         <v>201</v>
       </c>
       <c r="H59" s="1" t="str">
-        <f>LEFT(B59,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I59" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1057</v>
+      </c>
+      <c r="J59" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1057</v>
-      </c>
-      <c r="J59" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user103</v>
       </c>
-      <c r="K59" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K59" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L59" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L59" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>india</v>
       </c>
-      <c r="M59" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M59" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -4131,27 +4128,27 @@
         <v>226</v>
       </c>
       <c r="H60" s="1" t="str">
-        <f>LEFT(B60,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I60" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1058</v>
+      </c>
+      <c r="J60" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1058</v>
-      </c>
-      <c r="J60" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user150</v>
       </c>
-      <c r="K60" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K60" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L60" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L60" s="1" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M60" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M60" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -4178,27 +4175,27 @@
         <v>217</v>
       </c>
       <c r="H61" s="1" t="str">
-        <f>LEFT(B61,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I61" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1059</v>
+      </c>
+      <c r="J61" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1059</v>
-      </c>
-      <c r="J61" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user20@</v>
       </c>
-      <c r="K61" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K61" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L61" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L61" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>usa</v>
       </c>
-      <c r="M61" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M61" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -4218,28 +4215,28 @@
       <c r="G62" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="H62" s="1" t="str">
-        <f>LEFT(B62,3)</f>
+      <c r="H62" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1060</v>
+      </c>
+      <c r="J62" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>user112</v>
+      </c>
+      <c r="K62" s="1" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I62" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>1060</v>
-      </c>
-      <c r="J62" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>user112</v>
-      </c>
-      <c r="K62" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="L62" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L62" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>germany</v>
       </c>
-      <c r="M62" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M62" s="1" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4263,27 +4260,27 @@
         <v>209</v>
       </c>
       <c r="H63" s="1" t="str">
-        <f>LEFT(B63,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I63" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1061</v>
+      </c>
+      <c r="J63" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1061</v>
-      </c>
-      <c r="J63" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user31@</v>
       </c>
-      <c r="K63" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K63" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L63" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L63" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>australia</v>
       </c>
-      <c r="M63" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M63" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -4310,27 +4307,27 @@
         <v>228</v>
       </c>
       <c r="H64" s="1" t="str">
-        <f>LEFT(B64,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="4"/>
+        <v>Chris</v>
       </c>
       <c r="I64" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1062</v>
+      </c>
+      <c r="J64" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1062</v>
-      </c>
-      <c r="J64" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user71@</v>
       </c>
-      <c r="K64" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K64" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L64" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L64" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>uk</v>
       </c>
-      <c r="M64" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M64" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -4357,27 +4354,27 @@
         <v>229</v>
       </c>
       <c r="H65" s="1" t="str">
-        <f>LEFT(B65,3)</f>
+        <f t="shared" si="4"/>
         <v>Eve</v>
       </c>
       <c r="I65" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>1063</v>
+      </c>
+      <c r="J65" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1063</v>
-      </c>
-      <c r="J65" s="1" t="str">
-        <f t="shared" si="4"/>
         <v>user97@</v>
       </c>
-      <c r="K65" s="4" t="str">
-        <f t="shared" si="6"/>
+      <c r="K65" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L65" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="L65" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>usa</v>
       </c>
-      <c r="M65" s="4" t="str">
-        <f t="shared" si="8"/>
+      <c r="M65" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -4404,27 +4401,27 @@
         <v>230</v>
       </c>
       <c r="H66" s="1" t="str">
-        <f>LEFT(B66,3)</f>
-        <v>Joh</v>
+        <f t="shared" si="4"/>
+        <v>John</v>
       </c>
       <c r="I66" s="1" t="str">
-        <f t="shared" ref="I66:I97" si="9">RIGHT(A66,4)</f>
+        <f t="shared" ref="I66:I97" si="10">RIGHT(A66,4)</f>
         <v>1064</v>
       </c>
       <c r="J66" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user141</v>
       </c>
-      <c r="K66" s="4" t="str">
-        <f t="shared" ref="K66:K97" si="10">UPPER(B66)</f>
+      <c r="K66" s="1" t="str">
+        <f t="shared" ref="K66:K97" si="11">UPPER(B66)</f>
         <v>JOHN DOE</v>
       </c>
-      <c r="L66" s="4" t="str">
-        <f t="shared" ref="L66:L97" si="11">LOWER(D66)</f>
+      <c r="L66" s="1" t="str">
+        <f t="shared" ref="L66:L97" si="12">LOWER(D66)</f>
         <v>india</v>
       </c>
-      <c r="M66" s="4" t="str">
-        <f t="shared" ref="M66:M97" si="12">PROPER(K66)</f>
+      <c r="M66" s="1" t="str">
+        <f t="shared" ref="M66:M97" si="13">PROPER(K66)</f>
         <v>John Doe</v>
       </c>
     </row>
@@ -4451,27 +4448,27 @@
         <v>231</v>
       </c>
       <c r="H67" s="1" t="str">
-        <f>LEFT(B67,3)</f>
+        <f t="shared" si="4"/>
         <v>Sam</v>
       </c>
       <c r="I67" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1065</v>
       </c>
       <c r="J67" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>user125</v>
       </c>
-      <c r="K67" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="K67" s="1" t="str">
+        <f t="shared" si="11"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L67" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="L67" s="1" t="str">
+        <f t="shared" si="12"/>
         <v>india</v>
       </c>
-      <c r="M67" s="4" t="str">
-        <f t="shared" si="12"/>
+      <c r="M67" s="1" t="str">
+        <f t="shared" si="13"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -4495,27 +4492,27 @@
         <v>232</v>
       </c>
       <c r="H68" s="1" t="str">
-        <f t="shared" ref="H68:H131" si="13">LEFT(B68,3)</f>
+        <f t="shared" ref="H68:H131" si="14">IFERROR(LEFT(B68, FIND(" ", B68) - 1), B68)</f>
         <v>Sam</v>
       </c>
       <c r="I68" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1066</v>
       </c>
       <c r="J68" s="1" t="str">
-        <f t="shared" ref="J68:J131" si="14">MID(G68,1,7)</f>
+        <f t="shared" ref="J68:J131" si="15">MID(G68,1,7)</f>
         <v>user90@</v>
       </c>
-      <c r="K68" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="K68" s="1" t="str">
+        <f t="shared" si="11"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L68" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="L68" s="1" t="str">
+        <f t="shared" si="12"/>
         <v>australia</v>
       </c>
-      <c r="M68" s="4" t="str">
-        <f t="shared" si="12"/>
+      <c r="M68" s="1" t="str">
+        <f t="shared" si="13"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -4542,27 +4539,27 @@
         <v>233</v>
       </c>
       <c r="H69" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Alice</v>
+      </c>
+      <c r="I69" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1067</v>
+      </c>
+      <c r="J69" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user192</v>
+      </c>
+      <c r="K69" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>ALICE BROWN</v>
+      </c>
+      <c r="L69" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M69" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Ali</v>
-      </c>
-      <c r="I69" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1067</v>
-      </c>
-      <c r="J69" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user192</v>
-      </c>
-      <c r="K69" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>ALICE BROWN</v>
-      </c>
-      <c r="L69" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M69" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -4589,27 +4586,27 @@
         <v>195</v>
       </c>
       <c r="H70" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Sam</v>
+      </c>
+      <c r="I70" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1068</v>
+      </c>
+      <c r="J70" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user77@</v>
+      </c>
+      <c r="K70" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>SAM WILSON</v>
+      </c>
+      <c r="L70" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>uk</v>
+      </c>
+      <c r="M70" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Sam</v>
-      </c>
-      <c r="I70" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1068</v>
-      </c>
-      <c r="J70" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user77@</v>
-      </c>
-      <c r="K70" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>SAM WILSON</v>
-      </c>
-      <c r="L70" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>uk</v>
-      </c>
-      <c r="M70" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -4636,27 +4633,27 @@
         <v>234</v>
       </c>
       <c r="H71" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Bob</v>
+      </c>
+      <c r="I71" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1069</v>
+      </c>
+      <c r="J71" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user65@</v>
+      </c>
+      <c r="K71" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>BOB JOHNSON</v>
+      </c>
+      <c r="L71" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M71" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Bob</v>
-      </c>
-      <c r="I71" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1069</v>
-      </c>
-      <c r="J71" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user65@</v>
-      </c>
-      <c r="K71" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>BOB JOHNSON</v>
-      </c>
-      <c r="L71" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M71" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -4683,27 +4680,27 @@
         <v>176</v>
       </c>
       <c r="H72" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Eve</v>
+      </c>
+      <c r="I72" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1070</v>
+      </c>
+      <c r="J72" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>invalid</v>
+      </c>
+      <c r="K72" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>EVE ADAMS</v>
+      </c>
+      <c r="L72" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>australia</v>
+      </c>
+      <c r="M72" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Eve</v>
-      </c>
-      <c r="I72" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1070</v>
-      </c>
-      <c r="J72" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>invalid</v>
-      </c>
-      <c r="K72" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>EVE ADAMS</v>
-      </c>
-      <c r="L72" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>australia</v>
-      </c>
-      <c r="M72" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -4730,27 +4727,27 @@
         <v>235</v>
       </c>
       <c r="H73" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Eve</v>
+      </c>
+      <c r="I73" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1071</v>
+      </c>
+      <c r="J73" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user142</v>
+      </c>
+      <c r="K73" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>EVE ADAMS</v>
+      </c>
+      <c r="L73" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>usa</v>
+      </c>
+      <c r="M73" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Eve</v>
-      </c>
-      <c r="I73" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1071</v>
-      </c>
-      <c r="J73" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user142</v>
-      </c>
-      <c r="K73" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>EVE ADAMS</v>
-      </c>
-      <c r="L73" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>usa</v>
-      </c>
-      <c r="M73" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -4777,27 +4774,27 @@
         <v>184</v>
       </c>
       <c r="H74" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Bob</v>
+      </c>
+      <c r="I74" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1072</v>
+      </c>
+      <c r="J74" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user153</v>
+      </c>
+      <c r="K74" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>BOB JOHNSON</v>
+      </c>
+      <c r="L74" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M74" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Bob</v>
-      </c>
-      <c r="I74" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1072</v>
-      </c>
-      <c r="J74" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user153</v>
-      </c>
-      <c r="K74" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>BOB JOHNSON</v>
-      </c>
-      <c r="L74" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M74" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -4824,27 +4821,27 @@
         <v>228</v>
       </c>
       <c r="H75" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>John</v>
+      </c>
+      <c r="I75" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1073</v>
+      </c>
+      <c r="J75" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user71@</v>
+      </c>
+      <c r="K75" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>JOHN DOE</v>
+      </c>
+      <c r="L75" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M75" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Joh</v>
-      </c>
-      <c r="I75" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1073</v>
-      </c>
-      <c r="J75" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user71@</v>
-      </c>
-      <c r="K75" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>JOHN DOE</v>
-      </c>
-      <c r="L75" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M75" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -4868,27 +4865,27 @@
         <v>205</v>
       </c>
       <c r="H76" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Sam</v>
+      </c>
+      <c r="I76" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1074</v>
+      </c>
+      <c r="J76" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user143</v>
+      </c>
+      <c r="K76" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>SAM WILSON</v>
+      </c>
+      <c r="L76" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>germany</v>
+      </c>
+      <c r="M76" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Sam</v>
-      </c>
-      <c r="I76" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1074</v>
-      </c>
-      <c r="J76" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user143</v>
-      </c>
-      <c r="K76" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>SAM WILSON</v>
-      </c>
-      <c r="L76" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>germany</v>
-      </c>
-      <c r="M76" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -4911,28 +4908,28 @@
       <c r="G77" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H77" s="1" t="str">
+      <c r="H77" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I77" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1075</v>
+      </c>
+      <c r="J77" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user17@</v>
+      </c>
+      <c r="K77" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="L77" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="M77" s="1" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="I77" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1075</v>
-      </c>
-      <c r="J77" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user17@</v>
-      </c>
-      <c r="K77" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="L77" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="M77" s="4" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4959,27 +4956,27 @@
         <v>217</v>
       </c>
       <c r="H78" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Eve</v>
+      </c>
+      <c r="I78" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1076</v>
+      </c>
+      <c r="J78" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user20@</v>
+      </c>
+      <c r="K78" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>EVE ADAMS</v>
+      </c>
+      <c r="L78" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M78" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Eve</v>
-      </c>
-      <c r="I78" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1076</v>
-      </c>
-      <c r="J78" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user20@</v>
-      </c>
-      <c r="K78" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>EVE ADAMS</v>
-      </c>
-      <c r="L78" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M78" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -5003,27 +5000,27 @@
         <v>237</v>
       </c>
       <c r="H79" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Jane</v>
+      </c>
+      <c r="I79" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1077</v>
+      </c>
+      <c r="J79" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user22@</v>
+      </c>
+      <c r="K79" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>JANE SMITH</v>
+      </c>
+      <c r="L79" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>uk</v>
+      </c>
+      <c r="M79" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Jan</v>
-      </c>
-      <c r="I79" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1077</v>
-      </c>
-      <c r="J79" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user22@</v>
-      </c>
-      <c r="K79" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>JANE SMITH</v>
-      </c>
-      <c r="L79" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>uk</v>
-      </c>
-      <c r="M79" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -5047,27 +5044,27 @@
         <v>238</v>
       </c>
       <c r="H80" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Sam</v>
+      </c>
+      <c r="I80" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1078</v>
+      </c>
+      <c r="J80" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user46@</v>
+      </c>
+      <c r="K80" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>SAM WILSON</v>
+      </c>
+      <c r="L80" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>uk</v>
+      </c>
+      <c r="M80" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Sam</v>
-      </c>
-      <c r="I80" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1078</v>
-      </c>
-      <c r="J80" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user46@</v>
-      </c>
-      <c r="K80" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>SAM WILSON</v>
-      </c>
-      <c r="L80" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>uk</v>
-      </c>
-      <c r="M80" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -5094,27 +5091,27 @@
         <v>239</v>
       </c>
       <c r="H81" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Chris</v>
+      </c>
+      <c r="I81" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1079</v>
+      </c>
+      <c r="J81" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user55@</v>
+      </c>
+      <c r="K81" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>CHRIS LEE</v>
+      </c>
+      <c r="L81" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>usa</v>
+      </c>
+      <c r="M81" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Chr</v>
-      </c>
-      <c r="I81" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1079</v>
-      </c>
-      <c r="J81" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user55@</v>
-      </c>
-      <c r="K81" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>CHRIS LEE</v>
-      </c>
-      <c r="L81" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>usa</v>
-      </c>
-      <c r="M81" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -5138,27 +5135,27 @@
         <v>202</v>
       </c>
       <c r="H82" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Eve</v>
+      </c>
+      <c r="I82" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1080</v>
+      </c>
+      <c r="J82" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user135</v>
+      </c>
+      <c r="K82" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>EVE ADAMS</v>
+      </c>
+      <c r="L82" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M82" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Eve</v>
-      </c>
-      <c r="I82" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1080</v>
-      </c>
-      <c r="J82" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user135</v>
-      </c>
-      <c r="K82" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>EVE ADAMS</v>
-      </c>
-      <c r="L82" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M82" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -5185,27 +5182,27 @@
         <v>240</v>
       </c>
       <c r="H83" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Jane</v>
+      </c>
+      <c r="I83" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1081</v>
+      </c>
+      <c r="J83" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user156</v>
+      </c>
+      <c r="K83" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>JANE SMITH</v>
+      </c>
+      <c r="L83" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>usa</v>
+      </c>
+      <c r="M83" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Jan</v>
-      </c>
-      <c r="I83" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1081</v>
-      </c>
-      <c r="J83" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user156</v>
-      </c>
-      <c r="K83" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>JANE SMITH</v>
-      </c>
-      <c r="L83" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>usa</v>
-      </c>
-      <c r="M83" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -5232,27 +5229,27 @@
         <v>241</v>
       </c>
       <c r="H84" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Eve</v>
+      </c>
+      <c r="I84" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1082</v>
+      </c>
+      <c r="J84" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user104</v>
+      </c>
+      <c r="K84" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>EVE ADAMS</v>
+      </c>
+      <c r="L84" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>uk</v>
+      </c>
+      <c r="M84" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Eve</v>
-      </c>
-      <c r="I84" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1082</v>
-      </c>
-      <c r="J84" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user104</v>
-      </c>
-      <c r="K84" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>EVE ADAMS</v>
-      </c>
-      <c r="L84" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>uk</v>
-      </c>
-      <c r="M84" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -5279,27 +5276,27 @@
         <v>242</v>
       </c>
       <c r="H85" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Sam</v>
+      </c>
+      <c r="I85" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1083</v>
+      </c>
+      <c r="J85" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user145</v>
+      </c>
+      <c r="K85" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>SAM WILSON</v>
+      </c>
+      <c r="L85" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M85" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Sam</v>
-      </c>
-      <c r="I85" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1083</v>
-      </c>
-      <c r="J85" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user145</v>
-      </c>
-      <c r="K85" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>SAM WILSON</v>
-      </c>
-      <c r="L85" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M85" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -5326,27 +5323,27 @@
         <v>214</v>
       </c>
       <c r="H86" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>John</v>
+      </c>
+      <c r="I86" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1084</v>
+      </c>
+      <c r="J86" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user47@</v>
+      </c>
+      <c r="K86" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>JOHN DOE</v>
+      </c>
+      <c r="L86" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M86" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Joh</v>
-      </c>
-      <c r="I86" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1084</v>
-      </c>
-      <c r="J86" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user47@</v>
-      </c>
-      <c r="K86" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>JOHN DOE</v>
-      </c>
-      <c r="L86" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M86" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -5370,27 +5367,27 @@
         <v>243</v>
       </c>
       <c r="H87" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Chris</v>
+      </c>
+      <c r="I87" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1085</v>
+      </c>
+      <c r="J87" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user197</v>
+      </c>
+      <c r="K87" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>CHRIS LEE</v>
+      </c>
+      <c r="L87" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="M87" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Chr</v>
-      </c>
-      <c r="I87" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1085</v>
-      </c>
-      <c r="J87" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user197</v>
-      </c>
-      <c r="K87" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>CHRIS LEE</v>
-      </c>
-      <c r="L87" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="M87" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -5417,27 +5414,27 @@
         <v>244</v>
       </c>
       <c r="H88" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Chris</v>
+      </c>
+      <c r="I88" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1086</v>
+      </c>
+      <c r="J88" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user177</v>
+      </c>
+      <c r="K88" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>CHRIS LEE</v>
+      </c>
+      <c r="L88" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M88" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Chr</v>
-      </c>
-      <c r="I88" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1086</v>
-      </c>
-      <c r="J88" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user177</v>
-      </c>
-      <c r="K88" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>CHRIS LEE</v>
-      </c>
-      <c r="L88" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M88" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -5464,27 +5461,27 @@
         <v>197</v>
       </c>
       <c r="H89" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Sam</v>
+      </c>
+      <c r="I89" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1087</v>
+      </c>
+      <c r="J89" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user149</v>
+      </c>
+      <c r="K89" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>SAM WILSON</v>
+      </c>
+      <c r="L89" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>germany</v>
+      </c>
+      <c r="M89" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Sam</v>
-      </c>
-      <c r="I89" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1087</v>
-      </c>
-      <c r="J89" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user149</v>
-      </c>
-      <c r="K89" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>SAM WILSON</v>
-      </c>
-      <c r="L89" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>germany</v>
-      </c>
-      <c r="M89" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -5508,27 +5505,27 @@
         <v>245</v>
       </c>
       <c r="H90" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Chris</v>
+      </c>
+      <c r="I90" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1088</v>
+      </c>
+      <c r="J90" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user48@</v>
+      </c>
+      <c r="K90" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>CHRIS LEE</v>
+      </c>
+      <c r="L90" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="M90" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Chr</v>
-      </c>
-      <c r="I90" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1088</v>
-      </c>
-      <c r="J90" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user48@</v>
-      </c>
-      <c r="K90" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>CHRIS LEE</v>
-      </c>
-      <c r="L90" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="M90" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -5552,27 +5549,27 @@
         <v>197</v>
       </c>
       <c r="H91" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Jane</v>
+      </c>
+      <c r="I91" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1089</v>
+      </c>
+      <c r="J91" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user149</v>
+      </c>
+      <c r="K91" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>JANE SMITH</v>
+      </c>
+      <c r="L91" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>australia</v>
+      </c>
+      <c r="M91" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Jan</v>
-      </c>
-      <c r="I91" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1089</v>
-      </c>
-      <c r="J91" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user149</v>
-      </c>
-      <c r="K91" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>JANE SMITH</v>
-      </c>
-      <c r="L91" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>australia</v>
-      </c>
-      <c r="M91" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -5595,28 +5592,28 @@
       <c r="G92" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="H92" s="1" t="str">
+      <c r="H92" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I92" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1090</v>
+      </c>
+      <c r="J92" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user65@</v>
+      </c>
+      <c r="K92" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="L92" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>uk</v>
+      </c>
+      <c r="M92" s="1" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="I92" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1090</v>
-      </c>
-      <c r="J92" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user65@</v>
-      </c>
-      <c r="K92" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="L92" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>uk</v>
-      </c>
-      <c r="M92" s="4" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5643,27 +5640,27 @@
         <v>219</v>
       </c>
       <c r="H93" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Alice</v>
+      </c>
+      <c r="I93" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1091</v>
+      </c>
+      <c r="J93" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user43@</v>
+      </c>
+      <c r="K93" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>ALICE BROWN</v>
+      </c>
+      <c r="L93" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>australia</v>
+      </c>
+      <c r="M93" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Ali</v>
-      </c>
-      <c r="I93" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1091</v>
-      </c>
-      <c r="J93" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user43@</v>
-      </c>
-      <c r="K93" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>ALICE BROWN</v>
-      </c>
-      <c r="L93" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>australia</v>
-      </c>
-      <c r="M93" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -5687,27 +5684,27 @@
         <v>210</v>
       </c>
       <c r="H94" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Jane</v>
+      </c>
+      <c r="I94" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1092</v>
+      </c>
+      <c r="J94" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user98@</v>
+      </c>
+      <c r="K94" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>JANE SMITH</v>
+      </c>
+      <c r="L94" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="M94" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Jan</v>
-      </c>
-      <c r="I94" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1092</v>
-      </c>
-      <c r="J94" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user98@</v>
-      </c>
-      <c r="K94" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>JANE SMITH</v>
-      </c>
-      <c r="L94" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="M94" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -5731,27 +5728,27 @@
         <v>246</v>
       </c>
       <c r="H95" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Alice</v>
+      </c>
+      <c r="I95" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1093</v>
+      </c>
+      <c r="J95" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user102</v>
+      </c>
+      <c r="K95" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>ALICE BROWN</v>
+      </c>
+      <c r="L95" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>usa</v>
+      </c>
+      <c r="M95" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Ali</v>
-      </c>
-      <c r="I95" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1093</v>
-      </c>
-      <c r="J95" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user102</v>
-      </c>
-      <c r="K95" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>ALICE BROWN</v>
-      </c>
-      <c r="L95" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>usa</v>
-      </c>
-      <c r="M95" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -5778,27 +5775,27 @@
         <v>247</v>
       </c>
       <c r="H96" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Bob</v>
+      </c>
+      <c r="I96" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1094</v>
+      </c>
+      <c r="J96" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user148</v>
+      </c>
+      <c r="K96" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>BOB JOHNSON</v>
+      </c>
+      <c r="L96" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>india</v>
+      </c>
+      <c r="M96" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Bob</v>
-      </c>
-      <c r="I96" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1094</v>
-      </c>
-      <c r="J96" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user148</v>
-      </c>
-      <c r="K96" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>BOB JOHNSON</v>
-      </c>
-      <c r="L96" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>india</v>
-      </c>
-      <c r="M96" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -5825,27 +5822,27 @@
         <v>248</v>
       </c>
       <c r="H97" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>Alice</v>
+      </c>
+      <c r="I97" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>1095</v>
+      </c>
+      <c r="J97" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user155</v>
+      </c>
+      <c r="K97" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>ALICE BROWN</v>
+      </c>
+      <c r="L97" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>australia</v>
+      </c>
+      <c r="M97" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>Ali</v>
-      </c>
-      <c r="I97" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>1095</v>
-      </c>
-      <c r="J97" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user155</v>
-      </c>
-      <c r="K97" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>ALICE BROWN</v>
-      </c>
-      <c r="L97" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>australia</v>
-      </c>
-      <c r="M97" s="4" t="str">
-        <f t="shared" si="12"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -5872,27 +5869,27 @@
         <v>249</v>
       </c>
       <c r="H98" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Jan</v>
+        <f t="shared" si="14"/>
+        <v>Jane</v>
       </c>
       <c r="I98" s="1" t="str">
-        <f t="shared" ref="I98:I129" si="15">RIGHT(A98,4)</f>
+        <f t="shared" ref="I98:I129" si="16">RIGHT(A98,4)</f>
         <v>1096</v>
       </c>
       <c r="J98" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>user191</v>
       </c>
-      <c r="K98" s="4" t="str">
-        <f t="shared" ref="K98:K129" si="16">UPPER(B98)</f>
+      <c r="K98" s="1" t="str">
+        <f t="shared" ref="K98:K129" si="17">UPPER(B98)</f>
         <v>JANE SMITH</v>
       </c>
-      <c r="L98" s="4" t="str">
-        <f t="shared" ref="L98:L129" si="17">LOWER(D98)</f>
+      <c r="L98" s="1" t="str">
+        <f t="shared" ref="L98:L129" si="18">LOWER(D98)</f>
         <v>usa</v>
       </c>
-      <c r="M98" s="4" t="str">
-        <f t="shared" ref="M98:M129" si="18">PROPER(K98)</f>
+      <c r="M98" s="1" t="str">
+        <f t="shared" ref="M98:M129" si="19">PROPER(K98)</f>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -5919,27 +5916,27 @@
         <v>250</v>
       </c>
       <c r="H99" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Sam</v>
       </c>
       <c r="I99" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1097</v>
+      </c>
+      <c r="J99" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1097</v>
-      </c>
-      <c r="J99" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user113</v>
       </c>
-      <c r="K99" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K99" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L99" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L99" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>germany</v>
       </c>
-      <c r="M99" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M99" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -5966,27 +5963,27 @@
         <v>251</v>
       </c>
       <c r="H100" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Bob</v>
       </c>
       <c r="I100" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1098</v>
+      </c>
+      <c r="J100" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1098</v>
-      </c>
-      <c r="J100" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user62@</v>
       </c>
-      <c r="K100" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K100" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L100" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L100" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>australia</v>
       </c>
-      <c r="M100" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M100" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -6013,27 +6010,27 @@
         <v>252</v>
       </c>
       <c r="H101" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Eve</v>
       </c>
       <c r="I101" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1099</v>
+      </c>
+      <c r="J101" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1099</v>
-      </c>
-      <c r="J101" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user76@</v>
       </c>
-      <c r="K101" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K101" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L101" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L101" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>usa</v>
       </c>
-      <c r="M101" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M101" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -6060,27 +6057,27 @@
         <v>253</v>
       </c>
       <c r="H102" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Bob</v>
       </c>
       <c r="I102" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1100</v>
+      </c>
+      <c r="J102" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1100</v>
-      </c>
-      <c r="J102" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user40@</v>
       </c>
-      <c r="K102" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K102" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L102" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L102" s="1" t="str">
+        <f t="shared" si="18"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M102" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M102" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -6107,27 +6104,27 @@
         <v>194</v>
       </c>
       <c r="H103" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Bob</v>
       </c>
       <c r="I103" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1101</v>
+      </c>
+      <c r="J103" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1101</v>
-      </c>
-      <c r="J103" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user200</v>
       </c>
-      <c r="K103" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K103" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L103" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L103" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>germany</v>
       </c>
-      <c r="M103" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M103" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -6154,27 +6151,27 @@
         <v>254</v>
       </c>
       <c r="H104" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Ali</v>
+        <f t="shared" si="14"/>
+        <v>Alice</v>
       </c>
       <c r="I104" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1102</v>
+      </c>
+      <c r="J104" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1102</v>
-      </c>
-      <c r="J104" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user54@</v>
       </c>
-      <c r="K104" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K104" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L104" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L104" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>germany</v>
       </c>
-      <c r="M104" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M104" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -6198,27 +6195,27 @@
         <v>217</v>
       </c>
       <c r="H105" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Ali</v>
+        <f t="shared" si="14"/>
+        <v>Alice</v>
       </c>
       <c r="I105" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1103</v>
+      </c>
+      <c r="J105" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1103</v>
-      </c>
-      <c r="J105" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user20@</v>
       </c>
-      <c r="K105" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K105" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L105" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L105" s="1" t="str">
+        <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M105" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M105" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -6242,27 +6239,27 @@
         <v>253</v>
       </c>
       <c r="H106" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Jan</v>
+        <f t="shared" si="14"/>
+        <v>Jane</v>
       </c>
       <c r="I106" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1104</v>
+      </c>
+      <c r="J106" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1104</v>
-      </c>
-      <c r="J106" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user40@</v>
       </c>
-      <c r="K106" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K106" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>JANE SMITH</v>
       </c>
-      <c r="L106" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L106" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>australia</v>
       </c>
-      <c r="M106" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M106" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -6285,28 +6282,28 @@
       <c r="G107" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H107" s="1" t="str">
-        <f t="shared" si="13"/>
+      <c r="H107" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I107" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1105</v>
+      </c>
+      <c r="J107" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>invalid</v>
+      </c>
+      <c r="K107" s="1" t="str">
+        <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I107" s="1" t="str">
-        <f t="shared" si="15"/>
-        <v>1105</v>
-      </c>
-      <c r="J107" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>invalid</v>
-      </c>
-      <c r="K107" s="4" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="L107" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L107" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>uk</v>
       </c>
-      <c r="M107" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M107" s="1" t="str">
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6330,27 +6327,27 @@
         <v>255</v>
       </c>
       <c r="H108" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Eve</v>
       </c>
       <c r="I108" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1106</v>
+      </c>
+      <c r="J108" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1106</v>
-      </c>
-      <c r="J108" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user189</v>
       </c>
-      <c r="K108" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K108" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L108" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L108" s="1" t="str">
+        <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M108" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M108" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -6377,27 +6374,27 @@
         <v>196</v>
       </c>
       <c r="H109" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Sam</v>
       </c>
       <c r="I109" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1107</v>
+      </c>
+      <c r="J109" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1107</v>
-      </c>
-      <c r="J109" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user128</v>
       </c>
-      <c r="K109" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K109" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L109" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L109" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>australia</v>
       </c>
-      <c r="M109" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M109" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -6421,27 +6418,27 @@
         <v>256</v>
       </c>
       <c r="H110" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Sam</v>
       </c>
       <c r="I110" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1108</v>
+      </c>
+      <c r="J110" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1108</v>
-      </c>
-      <c r="J110" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user93@</v>
       </c>
-      <c r="K110" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K110" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>SAM WILSON</v>
       </c>
-      <c r="L110" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L110" s="1" t="str">
+        <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M110" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M110" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -6465,27 +6462,27 @@
         <v>257</v>
       </c>
       <c r="H111" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Jan</v>
+        <f t="shared" si="14"/>
+        <v>Jane</v>
       </c>
       <c r="I111" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1109</v>
+      </c>
+      <c r="J111" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1109</v>
-      </c>
-      <c r="J111" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user174</v>
       </c>
-      <c r="K111" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K111" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>JANE SMITH</v>
       </c>
-      <c r="L111" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L111" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>india</v>
       </c>
-      <c r="M111" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M111" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -6509,27 +6506,27 @@
         <v>258</v>
       </c>
       <c r="H112" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Chr</v>
+        <f t="shared" si="14"/>
+        <v>Chris</v>
       </c>
       <c r="I112" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1110</v>
+      </c>
+      <c r="J112" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1110</v>
-      </c>
-      <c r="J112" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user44@</v>
       </c>
-      <c r="K112" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K112" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L112" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L112" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>india</v>
       </c>
-      <c r="M112" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M112" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -6556,27 +6553,27 @@
         <v>233</v>
       </c>
       <c r="H113" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Chr</v>
+        <f t="shared" si="14"/>
+        <v>Chris</v>
       </c>
       <c r="I113" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1111</v>
+      </c>
+      <c r="J113" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1111</v>
-      </c>
-      <c r="J113" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user192</v>
       </c>
-      <c r="K113" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K113" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L113" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L113" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>usa</v>
       </c>
-      <c r="M113" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M113" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -6603,27 +6600,27 @@
         <v>252</v>
       </c>
       <c r="H114" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Eve</v>
       </c>
       <c r="I114" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1112</v>
+      </c>
+      <c r="J114" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1112</v>
-      </c>
-      <c r="J114" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user76@</v>
       </c>
-      <c r="K114" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K114" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L114" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L114" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>india</v>
       </c>
-      <c r="M114" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M114" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -6650,27 +6647,27 @@
         <v>259</v>
       </c>
       <c r="H115" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Ali</v>
+        <f t="shared" si="14"/>
+        <v>Alice</v>
       </c>
       <c r="I115" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1113</v>
+      </c>
+      <c r="J115" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1113</v>
-      </c>
-      <c r="J115" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user82@</v>
       </c>
-      <c r="K115" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K115" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L115" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L115" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>usa</v>
       </c>
-      <c r="M115" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M115" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -6697,27 +6694,27 @@
         <v>229</v>
       </c>
       <c r="H116" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Eve</v>
       </c>
       <c r="I116" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1114</v>
+      </c>
+      <c r="J116" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1114</v>
-      </c>
-      <c r="J116" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user97@</v>
       </c>
-      <c r="K116" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K116" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L116" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L116" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>uk</v>
       </c>
-      <c r="M116" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M116" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -6744,27 +6741,27 @@
         <v>197</v>
       </c>
       <c r="H117" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Bob</v>
       </c>
       <c r="I117" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1115</v>
+      </c>
+      <c r="J117" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1115</v>
-      </c>
-      <c r="J117" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user149</v>
       </c>
-      <c r="K117" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K117" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L117" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L117" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>germany</v>
       </c>
-      <c r="M117" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M117" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -6791,27 +6788,27 @@
         <v>233</v>
       </c>
       <c r="H118" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Bob</v>
       </c>
       <c r="I118" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1116</v>
+      </c>
+      <c r="J118" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1116</v>
-      </c>
-      <c r="J118" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user192</v>
       </c>
-      <c r="K118" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K118" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L118" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L118" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>australia</v>
       </c>
-      <c r="M118" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M118" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -6835,27 +6832,27 @@
         <v>260</v>
       </c>
       <c r="H119" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Bob</v>
       </c>
       <c r="I119" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1117</v>
+      </c>
+      <c r="J119" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1117</v>
-      </c>
-      <c r="J119" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user137</v>
       </c>
-      <c r="K119" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K119" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L119" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L119" s="1" t="str">
+        <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M119" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M119" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -6882,27 +6879,27 @@
         <v>261</v>
       </c>
       <c r="H120" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Chr</v>
+        <f t="shared" si="14"/>
+        <v>Chris</v>
       </c>
       <c r="I120" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1118</v>
+      </c>
+      <c r="J120" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1118</v>
-      </c>
-      <c r="J120" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user23@</v>
       </c>
-      <c r="K120" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K120" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L120" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L120" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>india</v>
       </c>
-      <c r="M120" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M120" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -6929,27 +6926,27 @@
         <v>194</v>
       </c>
       <c r="H121" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Eve</v>
       </c>
       <c r="I121" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1119</v>
+      </c>
+      <c r="J121" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1119</v>
-      </c>
-      <c r="J121" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user200</v>
       </c>
-      <c r="K121" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K121" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>EVE ADAMS</v>
       </c>
-      <c r="L121" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L121" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>australia</v>
       </c>
-      <c r="M121" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M121" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -6969,28 +6966,28 @@
       <c r="G122" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="H122" s="1" t="str">
-        <f t="shared" si="13"/>
+      <c r="H122" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I122" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1120</v>
+      </c>
+      <c r="J122" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>user101</v>
+      </c>
+      <c r="K122" s="1" t="str">
+        <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I122" s="1" t="str">
-        <f t="shared" si="15"/>
-        <v>1120</v>
-      </c>
-      <c r="J122" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>user101</v>
-      </c>
-      <c r="K122" s="4" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="L122" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L122" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>usa</v>
       </c>
-      <c r="M122" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M122" s="1" t="str">
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7017,27 +7014,27 @@
         <v>263</v>
       </c>
       <c r="H123" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Chr</v>
+        <f t="shared" si="14"/>
+        <v>Chris</v>
       </c>
       <c r="I123" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1121</v>
+      </c>
+      <c r="J123" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1121</v>
-      </c>
-      <c r="J123" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user132</v>
       </c>
-      <c r="K123" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K123" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L123" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L123" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>usa</v>
       </c>
-      <c r="M123" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M123" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -7064,27 +7061,27 @@
         <v>264</v>
       </c>
       <c r="H124" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Bob</v>
       </c>
       <c r="I124" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1122</v>
+      </c>
+      <c r="J124" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1122</v>
-      </c>
-      <c r="J124" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user171</v>
       </c>
-      <c r="K124" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K124" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L124" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L124" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>germany</v>
       </c>
-      <c r="M124" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M124" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -7108,27 +7105,27 @@
         <v>242</v>
       </c>
       <c r="H125" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Jan</v>
+        <f t="shared" si="14"/>
+        <v>Jane</v>
       </c>
       <c r="I125" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1123</v>
+      </c>
+      <c r="J125" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1123</v>
-      </c>
-      <c r="J125" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user145</v>
       </c>
-      <c r="K125" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K125" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>JANE SMITH</v>
       </c>
-      <c r="L125" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L125" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>germany</v>
       </c>
-      <c r="M125" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M125" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -7152,27 +7149,27 @@
         <v>265</v>
       </c>
       <c r="H126" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Joh</v>
+        <f t="shared" si="14"/>
+        <v>John</v>
       </c>
       <c r="I126" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1124</v>
+      </c>
+      <c r="J126" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1124</v>
-      </c>
-      <c r="J126" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user75@</v>
       </c>
-      <c r="K126" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K126" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>JOHN DOE</v>
       </c>
-      <c r="L126" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L126" s="1" t="str">
+        <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M126" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M126" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -7199,27 +7196,27 @@
         <v>266</v>
       </c>
       <c r="H127" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Joh</v>
+        <f t="shared" si="14"/>
+        <v>John</v>
       </c>
       <c r="I127" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1125</v>
+      </c>
+      <c r="J127" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1125</v>
-      </c>
-      <c r="J127" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user52@</v>
       </c>
-      <c r="K127" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K127" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>JOHN DOE</v>
       </c>
-      <c r="L127" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L127" s="1" t="str">
+        <f t="shared" si="18"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M127" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M127" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -7243,27 +7240,27 @@
         <v>267</v>
       </c>
       <c r="H128" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Bob</v>
       </c>
       <c r="I128" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1126</v>
+      </c>
+      <c r="J128" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1126</v>
-      </c>
-      <c r="J128" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user100</v>
       </c>
-      <c r="K128" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K128" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L128" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L128" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>germany</v>
       </c>
-      <c r="M128" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M128" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -7290,27 +7287,27 @@
         <v>203</v>
       </c>
       <c r="H129" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Joh</v>
+        <f t="shared" si="14"/>
+        <v>John</v>
       </c>
       <c r="I129" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>1127</v>
+      </c>
+      <c r="J129" s="1" t="str">
         <f t="shared" si="15"/>
-        <v>1127</v>
-      </c>
-      <c r="J129" s="1" t="str">
-        <f t="shared" si="14"/>
         <v>user83@</v>
       </c>
-      <c r="K129" s="4" t="str">
-        <f t="shared" si="16"/>
+      <c r="K129" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>JOHN DOE</v>
       </c>
-      <c r="L129" s="4" t="str">
-        <f t="shared" si="17"/>
+      <c r="L129" s="1" t="str">
+        <f t="shared" si="18"/>
         <v>usa</v>
       </c>
-      <c r="M129" s="4" t="str">
-        <f t="shared" si="18"/>
+      <c r="M129" s="1" t="str">
+        <f t="shared" si="19"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -7337,27 +7334,27 @@
         <v>268</v>
       </c>
       <c r="H130" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>Chr</v>
+        <f t="shared" si="14"/>
+        <v>Chris</v>
       </c>
       <c r="I130" s="1" t="str">
-        <f t="shared" ref="I130:I151" si="19">RIGHT(A130,4)</f>
+        <f t="shared" ref="I130:I151" si="20">RIGHT(A130,4)</f>
         <v>1128</v>
       </c>
       <c r="J130" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>user167</v>
       </c>
-      <c r="K130" s="4" t="str">
-        <f t="shared" ref="K130:K151" si="20">UPPER(B130)</f>
+      <c r="K130" s="1" t="str">
+        <f t="shared" ref="K130:K151" si="21">UPPER(B130)</f>
         <v>CHRIS LEE</v>
       </c>
-      <c r="L130" s="4" t="str">
-        <f t="shared" ref="L130:L151" si="21">LOWER(D130)</f>
+      <c r="L130" s="1" t="str">
+        <f t="shared" ref="L130:L151" si="22">LOWER(D130)</f>
         <v>usa</v>
       </c>
-      <c r="M130" s="4" t="str">
-        <f t="shared" ref="M130:M151" si="22">PROPER(K130)</f>
+      <c r="M130" s="1" t="str">
+        <f t="shared" ref="M130:M151" si="23">PROPER(K130)</f>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -7381,27 +7378,27 @@
         <v>215</v>
       </c>
       <c r="H131" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Bob</v>
       </c>
       <c r="I131" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1129</v>
       </c>
       <c r="J131" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>user175</v>
       </c>
-      <c r="K131" s="4" t="str">
-        <f t="shared" si="20"/>
+      <c r="K131" s="1" t="str">
+        <f t="shared" si="21"/>
         <v>BOB JOHNSON</v>
       </c>
-      <c r="L131" s="4" t="str">
-        <f t="shared" si="21"/>
+      <c r="L131" s="1" t="str">
+        <f t="shared" si="22"/>
         <v>uk</v>
       </c>
-      <c r="M131" s="4" t="str">
-        <f t="shared" si="22"/>
+      <c r="M131" s="1" t="str">
+        <f t="shared" si="23"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -7425,27 +7422,27 @@
         <v>183</v>
       </c>
       <c r="H132" s="1" t="str">
-        <f>LEFT(B132,3)</f>
-        <v>Ali</v>
+        <f t="shared" ref="H132:H151" si="24">IFERROR(LEFT(B132, FIND(" ", B132) - 1), B132)</f>
+        <v>Alice</v>
       </c>
       <c r="I132" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1130</v>
       </c>
       <c r="J132" s="1" t="str">
-        <f t="shared" ref="J132:J151" si="23">MID(G132,1,7)</f>
+        <f t="shared" ref="J132:J151" si="25">MID(G132,1,7)</f>
         <v>user25@</v>
       </c>
-      <c r="K132" s="4" t="str">
-        <f t="shared" si="20"/>
+      <c r="K132" s="1" t="str">
+        <f t="shared" si="21"/>
         <v>ALICE BROWN</v>
       </c>
-      <c r="L132" s="4" t="str">
-        <f t="shared" si="21"/>
+      <c r="L132" s="1" t="str">
+        <f t="shared" si="22"/>
         <v>india</v>
       </c>
-      <c r="M132" s="4" t="str">
-        <f t="shared" si="22"/>
+      <c r="M132" s="1" t="str">
+        <f t="shared" si="23"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -7472,27 +7469,27 @@
         <v>212</v>
       </c>
       <c r="H133" s="1" t="str">
-        <f>LEFT(B133,3)</f>
+        <f t="shared" si="24"/>
         <v>Sam</v>
       </c>
       <c r="I133" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1131</v>
       </c>
       <c r="J133" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user42@</v>
+      </c>
+      <c r="K133" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>SAM WILSON</v>
+      </c>
+      <c r="L133" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>germany</v>
+      </c>
+      <c r="M133" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user42@</v>
-      </c>
-      <c r="K133" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>SAM WILSON</v>
-      </c>
-      <c r="L133" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>germany</v>
-      </c>
-      <c r="M133" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -7519,27 +7516,27 @@
         <v>269</v>
       </c>
       <c r="H134" s="1" t="str">
-        <f>LEFT(B134,3)</f>
+        <f t="shared" si="24"/>
         <v>Eve</v>
       </c>
       <c r="I134" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1132</v>
       </c>
       <c r="J134" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user188</v>
+      </c>
+      <c r="K134" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>EVE ADAMS</v>
+      </c>
+      <c r="L134" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>usa</v>
+      </c>
+      <c r="M134" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user188</v>
-      </c>
-      <c r="K134" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>EVE ADAMS</v>
-      </c>
-      <c r="L134" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>usa</v>
-      </c>
-      <c r="M134" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -7566,27 +7563,27 @@
         <v>258</v>
       </c>
       <c r="H135" s="1" t="str">
-        <f>LEFT(B135,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="24"/>
+        <v>Chris</v>
       </c>
       <c r="I135" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1133</v>
       </c>
       <c r="J135" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user44@</v>
+      </c>
+      <c r="K135" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>CHRIS LEE</v>
+      </c>
+      <c r="L135" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>germany</v>
+      </c>
+      <c r="M135" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user44@</v>
-      </c>
-      <c r="K135" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>CHRIS LEE</v>
-      </c>
-      <c r="L135" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>germany</v>
-      </c>
-      <c r="M135" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -7613,27 +7610,27 @@
         <v>225</v>
       </c>
       <c r="H136" s="1" t="str">
-        <f>LEFT(B136,3)</f>
+        <f t="shared" si="24"/>
         <v>Eve</v>
       </c>
       <c r="I136" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1134</v>
       </c>
       <c r="J136" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user63@</v>
+      </c>
+      <c r="K136" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>EVE ADAMS</v>
+      </c>
+      <c r="L136" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>india</v>
+      </c>
+      <c r="M136" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user63@</v>
-      </c>
-      <c r="K136" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>EVE ADAMS</v>
-      </c>
-      <c r="L136" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>india</v>
-      </c>
-      <c r="M136" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -7656,28 +7653,28 @@
       <c r="G137" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H137" s="1" t="str">
-        <f>LEFT(B137,3)</f>
+      <c r="H137" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="I137" s="1" t="str">
+        <f t="shared" si="20"/>
+        <v>1135</v>
+      </c>
+      <c r="J137" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user198</v>
+      </c>
+      <c r="K137" s="1" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="I137" s="1" t="str">
-        <f t="shared" si="19"/>
-        <v>1135</v>
-      </c>
-      <c r="J137" s="1" t="str">
+      <c r="L137" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>uk</v>
+      </c>
+      <c r="M137" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user198</v>
-      </c>
-      <c r="K137" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="L137" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>uk</v>
-      </c>
-      <c r="M137" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -7704,27 +7701,27 @@
         <v>221</v>
       </c>
       <c r="H138" s="1" t="str">
-        <f>LEFT(B138,3)</f>
-        <v>Jan</v>
+        <f t="shared" si="24"/>
+        <v>Jane</v>
       </c>
       <c r="I138" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1136</v>
       </c>
       <c r="J138" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user59@</v>
+      </c>
+      <c r="K138" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>JANE SMITH</v>
+      </c>
+      <c r="L138" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>india</v>
+      </c>
+      <c r="M138" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user59@</v>
-      </c>
-      <c r="K138" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>JANE SMITH</v>
-      </c>
-      <c r="L138" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>india</v>
-      </c>
-      <c r="M138" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -7751,27 +7748,27 @@
         <v>270</v>
       </c>
       <c r="H139" s="1" t="str">
-        <f>LEFT(B139,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="24"/>
+        <v>Chris</v>
       </c>
       <c r="I139" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1137</v>
       </c>
       <c r="J139" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user165</v>
+      </c>
+      <c r="K139" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>CHRIS LEE</v>
+      </c>
+      <c r="L139" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>germany</v>
+      </c>
+      <c r="M139" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user165</v>
-      </c>
-      <c r="K139" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>CHRIS LEE</v>
-      </c>
-      <c r="L139" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>germany</v>
-      </c>
-      <c r="M139" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -7798,27 +7795,27 @@
         <v>189</v>
       </c>
       <c r="H140" s="1" t="str">
-        <f>LEFT(B140,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="24"/>
+        <v>Chris</v>
       </c>
       <c r="I140" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1138</v>
       </c>
       <c r="J140" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user3@e</v>
+      </c>
+      <c r="K140" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>CHRIS LEE</v>
+      </c>
+      <c r="L140" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>australia</v>
+      </c>
+      <c r="M140" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user3@e</v>
-      </c>
-      <c r="K140" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>CHRIS LEE</v>
-      </c>
-      <c r="L140" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>australia</v>
-      </c>
-      <c r="M140" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -7842,27 +7839,27 @@
         <v>237</v>
       </c>
       <c r="H141" s="1" t="str">
-        <f>LEFT(B141,3)</f>
+        <f t="shared" si="24"/>
         <v>Bob</v>
       </c>
       <c r="I141" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1139</v>
       </c>
       <c r="J141" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user22@</v>
+      </c>
+      <c r="K141" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>BOB JOHNSON</v>
+      </c>
+      <c r="L141" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="M141" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user22@</v>
-      </c>
-      <c r="K141" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>BOB JOHNSON</v>
-      </c>
-      <c r="L141" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="M141" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -7889,27 +7886,27 @@
         <v>176</v>
       </c>
       <c r="H142" s="1" t="str">
-        <f>LEFT(B142,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="24"/>
+        <v>Chris</v>
       </c>
       <c r="I142" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1140</v>
       </c>
       <c r="J142" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>invalid</v>
+      </c>
+      <c r="K142" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>CHRIS LEE</v>
+      </c>
+      <c r="L142" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>usa</v>
+      </c>
+      <c r="M142" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>invalid</v>
-      </c>
-      <c r="K142" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>CHRIS LEE</v>
-      </c>
-      <c r="L142" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>usa</v>
-      </c>
-      <c r="M142" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -7936,27 +7933,27 @@
         <v>201</v>
       </c>
       <c r="H143" s="1" t="str">
-        <f>LEFT(B143,3)</f>
-        <v>Jan</v>
+        <f t="shared" si="24"/>
+        <v>Jane</v>
       </c>
       <c r="I143" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1141</v>
       </c>
       <c r="J143" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user103</v>
+      </c>
+      <c r="K143" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>JANE SMITH</v>
+      </c>
+      <c r="L143" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>usa</v>
+      </c>
+      <c r="M143" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user103</v>
-      </c>
-      <c r="K143" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>JANE SMITH</v>
-      </c>
-      <c r="L143" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>usa</v>
-      </c>
-      <c r="M143" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Jane Smith</v>
       </c>
     </row>
@@ -7980,27 +7977,27 @@
         <v>206</v>
       </c>
       <c r="H144" s="1" t="str">
-        <f>LEFT(B144,3)</f>
-        <v>Ali</v>
+        <f t="shared" si="24"/>
+        <v>Alice</v>
       </c>
       <c r="I144" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1142</v>
       </c>
       <c r="J144" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user190</v>
+      </c>
+      <c r="K144" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>ALICE BROWN</v>
+      </c>
+      <c r="L144" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="M144" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user190</v>
-      </c>
-      <c r="K144" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>ALICE BROWN</v>
-      </c>
-      <c r="L144" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="M144" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Alice Brown</v>
       </c>
     </row>
@@ -8027,27 +8024,27 @@
         <v>271</v>
       </c>
       <c r="H145" s="1" t="str">
-        <f>LEFT(B145,3)</f>
-        <v>Chr</v>
+        <f t="shared" si="24"/>
+        <v>Chris</v>
       </c>
       <c r="I145" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1143</v>
       </c>
       <c r="J145" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user114</v>
+      </c>
+      <c r="K145" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>CHRIS LEE</v>
+      </c>
+      <c r="L145" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>uk</v>
+      </c>
+      <c r="M145" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user114</v>
-      </c>
-      <c r="K145" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>CHRIS LEE</v>
-      </c>
-      <c r="L145" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>uk</v>
-      </c>
-      <c r="M145" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Chris Lee</v>
       </c>
     </row>
@@ -8068,27 +8065,27 @@
         <v>272</v>
       </c>
       <c r="H146" s="1" t="str">
-        <f>LEFT(B146,3)</f>
+        <f t="shared" si="24"/>
         <v>Eve</v>
       </c>
       <c r="I146" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1144</v>
       </c>
       <c r="J146" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user53@</v>
+      </c>
+      <c r="K146" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>EVE ADAMS</v>
+      </c>
+      <c r="L146" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="M146" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user53@</v>
-      </c>
-      <c r="K146" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>EVE ADAMS</v>
-      </c>
-      <c r="L146" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="M146" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Eve Adams</v>
       </c>
     </row>
@@ -8115,27 +8112,27 @@
         <v>269</v>
       </c>
       <c r="H147" s="1" t="str">
-        <f>LEFT(B147,3)</f>
+        <f t="shared" si="24"/>
         <v>Sam</v>
       </c>
       <c r="I147" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1145</v>
       </c>
       <c r="J147" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user188</v>
+      </c>
+      <c r="K147" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>SAM WILSON</v>
+      </c>
+      <c r="L147" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>australia</v>
+      </c>
+      <c r="M147" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user188</v>
-      </c>
-      <c r="K147" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>SAM WILSON</v>
-      </c>
-      <c r="L147" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>australia</v>
-      </c>
-      <c r="M147" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -8162,27 +8159,27 @@
         <v>270</v>
       </c>
       <c r="H148" s="1" t="str">
-        <f>LEFT(B148,3)</f>
-        <v>Joh</v>
+        <f t="shared" si="24"/>
+        <v>John</v>
       </c>
       <c r="I148" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1146</v>
       </c>
       <c r="J148" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user165</v>
+      </c>
+      <c r="K148" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>JOHN DOE</v>
+      </c>
+      <c r="L148" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>usa</v>
+      </c>
+      <c r="M148" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user165</v>
-      </c>
-      <c r="K148" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>JOHN DOE</v>
-      </c>
-      <c r="L148" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>usa</v>
-      </c>
-      <c r="M148" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>John Doe</v>
       </c>
     </row>
@@ -8209,27 +8206,27 @@
         <v>273</v>
       </c>
       <c r="H149" s="1" t="str">
-        <f>LEFT(B149,3)</f>
+        <f t="shared" si="24"/>
         <v>Bob</v>
       </c>
       <c r="I149" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1147</v>
       </c>
       <c r="J149" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user163</v>
+      </c>
+      <c r="K149" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>BOB JOHNSON</v>
+      </c>
+      <c r="L149" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>australia</v>
+      </c>
+      <c r="M149" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user163</v>
-      </c>
-      <c r="K149" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>BOB JOHNSON</v>
-      </c>
-      <c r="L149" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>australia</v>
-      </c>
-      <c r="M149" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -8253,27 +8250,27 @@
         <v>227</v>
       </c>
       <c r="H150" s="1" t="str">
-        <f>LEFT(B150,3)</f>
+        <f t="shared" si="24"/>
         <v>Bob</v>
       </c>
       <c r="I150" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1148</v>
       </c>
       <c r="J150" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user112</v>
+      </c>
+      <c r="K150" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>BOB JOHNSON</v>
+      </c>
+      <c r="L150" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>uk</v>
+      </c>
+      <c r="M150" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user112</v>
-      </c>
-      <c r="K150" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>BOB JOHNSON</v>
-      </c>
-      <c r="L150" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>uk</v>
-      </c>
-      <c r="M150" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Bob Johnson</v>
       </c>
     </row>
@@ -8300,27 +8297,27 @@
         <v>274</v>
       </c>
       <c r="H151" s="1" t="str">
-        <f>LEFT(B151,3)</f>
+        <f t="shared" si="24"/>
         <v>Sam</v>
       </c>
       <c r="I151" s="1" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1149</v>
       </c>
       <c r="J151" s="1" t="str">
+        <f t="shared" si="25"/>
+        <v>user30@</v>
+      </c>
+      <c r="K151" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>SAM WILSON</v>
+      </c>
+      <c r="L151" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>india</v>
+      </c>
+      <c r="M151" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>user30@</v>
-      </c>
-      <c r="K151" s="4" t="str">
-        <f t="shared" si="20"/>
-        <v>SAM WILSON</v>
-      </c>
-      <c r="L151" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>india</v>
-      </c>
-      <c r="M151" s="4" t="str">
-        <f t="shared" si="22"/>
         <v>Sam Wilson</v>
       </c>
     </row>
@@ -8337,55 +8334,55 @@
   <dimension ref="A4:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="73.5546875" customWidth="1"/>
+    <col min="2" max="2" width="106.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
     <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>280</v>
+      <c r="B6" s="4" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>285</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>286</v>
       </c>
     </row>
   </sheetData>
